--- a/database/event/4314/event_4314_evp_summary.xlsx
+++ b/database/event/4314/event_4314_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3119</v>
+        <v>8.2568</v>
       </c>
       <c r="C2" t="n">
-        <v>1.1504</v>
+        <v>1.1428</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9365</v>
+        <v>2.8456</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3119</v>
+        <v>8.2568</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1765</v>
+        <v>5.1214</v>
       </c>
       <c r="G2" t="n">
         <v>3.1354</v>
       </c>
       <c r="H2" t="n">
-        <v>5.8136</v>
+        <v>5.7273</v>
       </c>
       <c r="I2" t="n">
         <v>5.9226</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.8895</v>
+        <v>7.8499</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0919</v>
+        <v>1.0865</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7658</v>
+        <v>2.6835</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8895</v>
+        <v>7.8499</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5526</v>
+        <v>3.513</v>
       </c>
       <c r="G3" t="n">
         <v>4.3368</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5526</v>
+        <v>3.513</v>
       </c>
       <c r="I3" t="n">
         <v>3.6025</v>
@@ -594,7 +594,7 @@
         <v>0.9236</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2745</v>
+        <v>2.2148</v>
       </c>
       <c r="E4" t="n">
         <v>6.6734</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0776</v>
+        <v>6.0298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8345</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0339</v>
+        <v>1.9584</v>
       </c>
       <c r="E5" t="n">
-        <v>6.0776</v>
+        <v>6.0298</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6873</v>
+        <v>4.6395</v>
       </c>
       <c r="G5" t="n">
         <v>1.3903</v>
       </c>
       <c r="H5" t="n">
-        <v>5.0466</v>
+        <v>4.9717</v>
       </c>
       <c r="I5" t="n">
         <v>5.1412</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9532</v>
+        <v>5.9006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8239</v>
+        <v>0.8167</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9836</v>
+        <v>1.9069</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9532</v>
+        <v>5.9006</v>
       </c>
       <c r="F6" t="n">
-        <v>5.0129</v>
+        <v>4.9603</v>
       </c>
       <c r="G6" t="n">
         <v>0.9403</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5571</v>
+        <v>5.4747</v>
       </c>
       <c r="I6" t="n">
         <v>5.6613</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6905</v>
+        <v>5.6511</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7876</v>
+        <v>0.7821</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8775</v>
+        <v>1.8075</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6905</v>
+        <v>5.6511</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1191</v>
+        <v>4.0798</v>
       </c>
       <c r="G7" t="n">
         <v>1.5714</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1557</v>
+        <v>4.094</v>
       </c>
       <c r="I7" t="n">
         <v>4.2336</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.4718</v>
+        <v>5.4205</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7573</v>
+        <v>0.7502</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7891</v>
+        <v>1.7156</v>
       </c>
       <c r="E8" t="n">
-        <v>5.4718</v>
+        <v>5.4205</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9261</v>
+        <v>4.8748</v>
       </c>
       <c r="G8" t="n">
         <v>0.5457</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4211</v>
+        <v>5.3407</v>
       </c>
       <c r="I8" t="n">
         <v>5.5228</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.1631</v>
+        <v>5.1231</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7146</v>
+        <v>0.7091</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6644</v>
+        <v>1.5971</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1631</v>
+        <v>5.1231</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5897</v>
+        <v>3.5497</v>
       </c>
       <c r="G9" t="n">
         <v>1.5734</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5897</v>
+        <v>3.5497</v>
       </c>
       <c r="I9" t="n">
         <v>3.64</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.004</v>
+        <v>4.9368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6926</v>
+        <v>0.6833</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6001</v>
+        <v>1.5229</v>
       </c>
       <c r="E10" t="n">
-        <v>5.004</v>
+        <v>4.9368</v>
       </c>
       <c r="F10" t="n">
-        <v>5.0999</v>
+        <v>5.0327</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0959</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6936</v>
+        <v>5.5882</v>
       </c>
       <c r="I10" t="n">
         <v>5.8274</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.8579</v>
+        <v>4.8161</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6724</v>
+        <v>0.6666</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5411</v>
+        <v>1.4748</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8579</v>
+        <v>4.8161</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2848</v>
+        <v>4.243</v>
       </c>
       <c r="G11" t="n">
         <v>0.5731000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4155</v>
+        <v>4.35</v>
       </c>
       <c r="I11" t="n">
         <v>4.4983</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.5048</v>
+        <v>4.4437</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.615</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3985</v>
+        <v>1.3265</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5048</v>
+        <v>4.4437</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7681</v>
+        <v>4.707</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2633</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1733</v>
+        <v>5.0775</v>
       </c>
       <c r="I12" t="n">
         <v>5.2948</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.2462</v>
+        <v>4.1958</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5877</v>
+        <v>0.5807</v>
       </c>
       <c r="D13" t="n">
-        <v>1.294</v>
+        <v>1.2277</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2462</v>
+        <v>4.1958</v>
       </c>
       <c r="F13" t="n">
-        <v>4.867</v>
+        <v>4.8166</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6208</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3285</v>
+        <v>5.2494</v>
       </c>
       <c r="I13" t="n">
         <v>5.4284</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.1677</v>
+        <v>4.1426</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5768</v>
+        <v>0.5734</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2623</v>
+        <v>1.2065</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1677</v>
+        <v>4.1426</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3826</v>
+        <v>3.3575</v>
       </c>
       <c r="G14" t="n">
         <v>0.7851</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3826</v>
+        <v>3.3575</v>
       </c>
       <c r="I14" t="n">
         <v>3.4142</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.1542</v>
+        <v>4.1354</v>
       </c>
       <c r="C15" t="n">
-        <v>0.575</v>
+        <v>0.5724</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2568</v>
+        <v>1.2036</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1542</v>
+        <v>4.1354</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6827</v>
+        <v>1.6639</v>
       </c>
       <c r="G15" t="n">
         <v>2.4715</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6827</v>
+        <v>1.6639</v>
       </c>
       <c r="I15" t="n">
         <v>1.7063</v>
@@ -1146,7 +1146,7 @@
         <v>0.5657</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2299</v>
+        <v>1.1846</v>
       </c>
       <c r="E16" t="n">
         <v>4.0875</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.0171</v>
+        <v>3.9919</v>
       </c>
       <c r="C17" t="n">
-        <v>0.556</v>
+        <v>0.5525</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2015</v>
+        <v>1.1465</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0171</v>
+        <v>3.9919</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3922</v>
+        <v>3.367</v>
       </c>
       <c r="G17" t="n">
         <v>0.6249</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3922</v>
+        <v>3.367</v>
       </c>
       <c r="I17" t="n">
         <v>3.4239</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foxz</t>
+          <t>Papichulo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.8678</v>
+        <v>3.8482</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5353</v>
+        <v>0.5326</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1411</v>
+        <v>1.0892</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8678</v>
+        <v>3.8482</v>
       </c>
       <c r="F18" t="n">
-        <v>3.8678</v>
+        <v>3.8482</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8678</v>
+        <v>3.8482</v>
       </c>
       <c r="I18" t="n">
-        <v>3.922</v>
+        <v>3.8806</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.922</v>
+        <v>3.8806</v>
       </c>
       <c r="N18" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Papichulo</t>
+          <t>foxz</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.8627</v>
+        <v>3.8247</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5346</v>
+        <v>0.5294</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1391</v>
+        <v>1.0799</v>
       </c>
       <c r="E19" t="n">
-        <v>3.8627</v>
+        <v>3.8247</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8627</v>
+        <v>3.8247</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8627</v>
+        <v>3.8247</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8806</v>
+        <v>3.922</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8806</v>
+        <v>3.922</v>
       </c>
       <c r="N19" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.8149</v>
+        <v>3.7788</v>
       </c>
       <c r="C20" t="n">
-        <v>0.528</v>
+        <v>0.523</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1198</v>
+        <v>1.0616</v>
       </c>
       <c r="E20" t="n">
-        <v>3.8149</v>
+        <v>3.7788</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2444</v>
+        <v>3.2083</v>
       </c>
       <c r="G20" t="n">
         <v>0.5705</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2444</v>
+        <v>3.2083</v>
       </c>
       <c r="I20" t="n">
         <v>3.2899</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.6469</v>
+        <v>3.6197</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5047</v>
+        <v>0.501</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0519</v>
+        <v>0.9982</v>
       </c>
       <c r="E21" t="n">
-        <v>3.6469</v>
+        <v>3.6197</v>
       </c>
       <c r="F21" t="n">
-        <v>3.6469</v>
+        <v>3.6197</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6469</v>
+        <v>3.6197</v>
       </c>
       <c r="I21" t="n">
         <v>3.6809</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.6302</v>
+        <v>3.6155</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5024</v>
+        <v>0.5004</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0452</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.6302</v>
+        <v>3.6155</v>
       </c>
       <c r="F22" t="n">
-        <v>1.9706</v>
+        <v>1.9559</v>
       </c>
       <c r="G22" t="n">
         <v>1.6596</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9706</v>
+        <v>1.9559</v>
       </c>
       <c r="I22" t="n">
         <v>1.989</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.6272</v>
+        <v>3.582</v>
       </c>
       <c r="C23" t="n">
-        <v>0.502</v>
+        <v>0.4958</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0439</v>
+        <v>0.9832</v>
       </c>
       <c r="E23" t="n">
-        <v>3.6272</v>
+        <v>3.582</v>
       </c>
       <c r="F23" t="n">
-        <v>4.5195</v>
+        <v>4.4743</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8923</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7836</v>
+        <v>4.7126</v>
       </c>
       <c r="I23" t="n">
         <v>4.8733</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.5314</v>
+        <v>3.4874</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4888</v>
+        <v>0.4827</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0052</v>
+        <v>0.9455</v>
       </c>
       <c r="E24" t="n">
-        <v>3.5314</v>
+        <v>3.4874</v>
       </c>
       <c r="F24" t="n">
-        <v>2.9677</v>
+        <v>2.9237</v>
       </c>
       <c r="G24" t="n">
         <v>0.5637</v>
       </c>
       <c r="H24" t="n">
-        <v>2.9677</v>
+        <v>2.9237</v>
       </c>
       <c r="I24" t="n">
         <v>3.0234</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.2696</v>
+        <v>3.2624</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4525</v>
+        <v>0.4515</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8995</v>
+        <v>0.8558</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2696</v>
+        <v>3.2624</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9707</v>
+        <v>0.9635</v>
       </c>
       <c r="G25" t="n">
         <v>2.299</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9707</v>
+        <v>0.9635</v>
       </c>
       <c r="I25" t="n">
         <v>0.9798</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1391</v>
+        <v>3.1274</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4345</v>
+        <v>0.4328</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8468</v>
+        <v>0.802</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1391</v>
+        <v>3.1274</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1391</v>
+        <v>3.1274</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1391</v>
+        <v>3.1274</v>
       </c>
       <c r="I26" t="n">
         <v>3.1537</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.1013</v>
+        <v>3.077</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4292</v>
+        <v>0.4259</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8315</v>
+        <v>0.782</v>
       </c>
       <c r="E27" t="n">
-        <v>3.1013</v>
+        <v>3.077</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2704</v>
+        <v>3.2461</v>
       </c>
       <c r="G27" t="n">
         <v>-0.1691</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2704</v>
+        <v>3.2461</v>
       </c>
       <c r="I27" t="n">
         <v>3.3009</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.0202</v>
+        <v>2.9865</v>
       </c>
       <c r="C28" t="n">
-        <v>0.418</v>
+        <v>0.4133</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7987</v>
+        <v>0.7459</v>
       </c>
       <c r="E28" t="n">
-        <v>3.0202</v>
+        <v>2.9865</v>
       </c>
       <c r="F28" t="n">
-        <v>3.0202</v>
+        <v>2.9865</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.0202</v>
+        <v>2.9865</v>
       </c>
       <c r="I28" t="n">
         <v>3.0626</v>
@@ -1744,7 +1744,7 @@
         <v>0.4104</v>
       </c>
       <c r="D29" t="n">
-        <v>0.7766</v>
+        <v>0.7375</v>
       </c>
       <c r="E29" t="n">
         <v>2.9654</v>
@@ -1790,7 +1790,7 @@
         <v>0.4087</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7326</v>
       </c>
       <c r="E30" t="n">
         <v>2.9532</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.8645</v>
+        <v>2.8546</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3965</v>
+        <v>0.3951</v>
       </c>
       <c r="D31" t="n">
-        <v>0.7358</v>
+        <v>0.6934</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8645</v>
+        <v>2.8546</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3288</v>
+        <v>1.3189</v>
       </c>
       <c r="G31" t="n">
         <v>1.5357</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3288</v>
+        <v>1.3189</v>
       </c>
       <c r="I31" t="n">
         <v>1.3412</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.7992</v>
+        <v>2.768</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3874</v>
+        <v>0.3831</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7095</v>
+        <v>0.6589</v>
       </c>
       <c r="E32" t="n">
-        <v>2.7992</v>
+        <v>2.768</v>
       </c>
       <c r="F32" t="n">
-        <v>2.7992</v>
+        <v>2.768</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.7992</v>
+        <v>2.768</v>
       </c>
       <c r="I32" t="n">
         <v>2.8385</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.779</v>
+        <v>2.7481</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3846</v>
+        <v>0.3803</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7013</v>
+        <v>0.6509</v>
       </c>
       <c r="E33" t="n">
-        <v>2.779</v>
+        <v>2.7481</v>
       </c>
       <c r="F33" t="n">
-        <v>2.779</v>
+        <v>2.7481</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.779</v>
+        <v>2.7481</v>
       </c>
       <c r="I33" t="n">
         <v>2.818</v>
@@ -1974,7 +1974,7 @@
         <v>0.3714</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6626</v>
+        <v>0.6251</v>
       </c>
       <c r="E34" t="n">
         <v>2.6832</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.5612</v>
+        <v>2.5517</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3545</v>
+        <v>0.3532</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6133</v>
+        <v>0.5727</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5612</v>
+        <v>2.5517</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5612</v>
+        <v>2.5517</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.5612</v>
+        <v>2.5517</v>
       </c>
       <c r="I35" t="n">
         <v>2.5731</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LETN1</t>
+          <t>scoobyxie</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.4946</v>
+        <v>2.4478</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3453</v>
+        <v>0.3388</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5864</v>
+        <v>0.5313</v>
       </c>
       <c r="E36" t="n">
-        <v>2.4946</v>
+        <v>2.4478</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1133</v>
+        <v>2.4478</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.6187</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1133</v>
+        <v>2.4478</v>
       </c>
       <c r="I36" t="n">
-        <v>3.1864</v>
+        <v>2.5102</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6187</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="L36" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.5677</v>
+        <v>2.5102</v>
       </c>
       <c r="N36" t="n">
-        <v>282</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>scoobyxie</t>
+          <t>LETN1</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.4755</v>
+        <v>2.437</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3426</v>
+        <v>0.3373</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5787</v>
+        <v>0.527</v>
       </c>
       <c r="E37" t="n">
-        <v>2.4755</v>
+        <v>2.437</v>
       </c>
       <c r="F37" t="n">
-        <v>2.4755</v>
+        <v>3.0557</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.6187</v>
       </c>
       <c r="H37" t="n">
-        <v>2.4755</v>
+        <v>3.0557</v>
       </c>
       <c r="I37" t="n">
-        <v>2.5102</v>
+        <v>3.1864</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.6187</v>
       </c>
       <c r="K37" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M37" t="n">
-        <v>2.5102</v>
+        <v>2.5677</v>
       </c>
       <c r="N37" t="n">
-        <v>200</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38">
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.0627</v>
+        <v>2.006</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2855</v>
+        <v>0.2776</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4119</v>
+        <v>0.3553</v>
       </c>
       <c r="E38" t="n">
-        <v>2.0627</v>
+        <v>2.006</v>
       </c>
       <c r="F38" t="n">
-        <v>3.0627</v>
+        <v>3.006</v>
       </c>
       <c r="G38" t="n">
         <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>3.0627</v>
+        <v>3.006</v>
       </c>
       <c r="I38" t="n">
         <v>3.1346</v>
@@ -2204,7 +2204,7 @@
         <v>0.2674</v>
       </c>
       <c r="D39" t="n">
-        <v>0.3592</v>
+        <v>0.3258</v>
       </c>
       <c r="E39" t="n">
         <v>1.9321</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9186</v>
+        <v>1.901</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2655</v>
+        <v>0.2631</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3537</v>
+        <v>0.3134</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9186</v>
+        <v>1.901</v>
       </c>
       <c r="F40" t="n">
-        <v>2.3727</v>
+        <v>2.3551</v>
       </c>
       <c r="G40" t="n">
         <v>-0.4541</v>
       </c>
       <c r="H40" t="n">
-        <v>2.3727</v>
+        <v>2.3551</v>
       </c>
       <c r="I40" t="n">
         <v>2.3949</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.863</v>
+        <v>1.8561</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2578</v>
+        <v>0.2569</v>
       </c>
       <c r="D41" t="n">
-        <v>0.3312</v>
+        <v>0.2956</v>
       </c>
       <c r="E41" t="n">
-        <v>1.863</v>
+        <v>1.8561</v>
       </c>
       <c r="F41" t="n">
-        <v>1.863</v>
+        <v>1.8561</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.863</v>
+        <v>1.8561</v>
       </c>
       <c r="I41" t="n">
         <v>1.8717</v>
@@ -2342,7 +2342,7 @@
         <v>0.256</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3259</v>
+        <v>0.2931</v>
       </c>
       <c r="E42" t="n">
         <v>1.8498</v>
@@ -2388,7 +2388,7 @@
         <v>0.2515</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3129</v>
+        <v>0.2802</v>
       </c>
       <c r="E43" t="n">
         <v>1.8175</v>
@@ -2424,93 +2424,93 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>stk</t>
+          <t>floppy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.7658</v>
+        <v>1.7576</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2444</v>
+        <v>0.2433</v>
       </c>
       <c r="D44" t="n">
-        <v>0.292</v>
+        <v>0.2563</v>
       </c>
       <c r="E44" t="n">
-        <v>1.7658</v>
+        <v>1.7576</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7658</v>
+        <v>1.7576</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7658</v>
+        <v>1.7576</v>
       </c>
       <c r="I44" t="n">
-        <v>1.7906</v>
+        <v>1.7576</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7906</v>
+        <v>1.7576</v>
       </c>
       <c r="N44" t="n">
-        <v>182</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>floppy</t>
+          <t>stk</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.7576</v>
+        <v>1.7461</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2433</v>
+        <v>0.2417</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2887</v>
+        <v>0.2517</v>
       </c>
       <c r="E45" t="n">
-        <v>1.7576</v>
+        <v>1.7461</v>
       </c>
       <c r="F45" t="n">
-        <v>1.7576</v>
+        <v>1.7461</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.7576</v>
+        <v>1.7461</v>
       </c>
       <c r="I45" t="n">
-        <v>1.7576</v>
+        <v>1.7906</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.7576</v>
+        <v>1.7906</v>
       </c>
       <c r="N45" t="n">
-        <v>138</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.7217</v>
+        <v>1.7025</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2383</v>
+        <v>0.2356</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2742</v>
+        <v>0.2344</v>
       </c>
       <c r="E46" t="n">
-        <v>1.7217</v>
+        <v>1.7025</v>
       </c>
       <c r="F46" t="n">
-        <v>1.7217</v>
+        <v>1.7025</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.7217</v>
+        <v>1.7025</v>
       </c>
       <c r="I46" t="n">
         <v>1.7458</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.7161</v>
+        <v>1.6781</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2375</v>
+        <v>0.2323</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2719</v>
+        <v>0.2246</v>
       </c>
       <c r="E47" t="n">
-        <v>1.7161</v>
+        <v>1.6781</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5616</v>
+        <v>2.5236</v>
       </c>
       <c r="G47" t="n">
         <v>-0.8455</v>
       </c>
       <c r="H47" t="n">
-        <v>2.5616</v>
+        <v>2.5236</v>
       </c>
       <c r="I47" t="n">
         <v>2.6096</v>
@@ -2608,93 +2608,93 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>witz</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.6208</v>
+        <v>1.5907</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2243</v>
+        <v>0.2202</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2334</v>
+        <v>0.1898</v>
       </c>
       <c r="E48" t="n">
-        <v>1.6208</v>
+        <v>1.5907</v>
       </c>
       <c r="F48" t="n">
-        <v>1.6553</v>
+        <v>1.5907</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0345</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.6553</v>
+        <v>1.5907</v>
       </c>
       <c r="I48" t="n">
-        <v>1.6942</v>
+        <v>1.604</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.0345</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L48" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.6597</v>
+        <v>1.604</v>
       </c>
       <c r="N48" t="n">
-        <v>282</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>witz</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.5966</v>
+        <v>1.5902</v>
       </c>
       <c r="C49" t="n">
-        <v>0.221</v>
+        <v>0.2201</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2236</v>
+        <v>0.1896</v>
       </c>
       <c r="E49" t="n">
-        <v>1.5966</v>
+        <v>1.5902</v>
       </c>
       <c r="F49" t="n">
-        <v>1.5966</v>
+        <v>1.6247</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-0.0345</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5966</v>
+        <v>1.6247</v>
       </c>
       <c r="I49" t="n">
-        <v>1.604</v>
+        <v>1.6942</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-0.0345</v>
       </c>
       <c r="K49" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M49" t="n">
-        <v>1.604</v>
+        <v>1.6597</v>
       </c>
       <c r="N49" t="n">
-        <v>207</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50">
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.4065</v>
+        <v>1.4008</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1947</v>
+        <v>0.1939</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1468</v>
+        <v>0.1142</v>
       </c>
       <c r="E50" t="n">
-        <v>1.4065</v>
+        <v>1.4008</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7498</v>
       </c>
       <c r="G50" t="n">
         <v>0.651</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7498</v>
       </c>
       <c r="I50" t="n">
         <v>0.7625</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.3483</v>
+        <v>1.3143</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1866</v>
+        <v>0.1819</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1233</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>1.3483</v>
+        <v>1.3143</v>
       </c>
       <c r="F51" t="n">
-        <v>2.2932</v>
+        <v>2.2592</v>
       </c>
       <c r="G51" t="n">
         <v>-0.9449</v>
       </c>
       <c r="H51" t="n">
-        <v>2.2932</v>
+        <v>2.2592</v>
       </c>
       <c r="I51" t="n">
         <v>2.3362</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.2881</v>
+        <v>1.2603</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1783</v>
+        <v>0.1744</v>
       </c>
       <c r="D52" t="n">
-        <v>0.099</v>
+        <v>0.0582</v>
       </c>
       <c r="E52" t="n">
-        <v>1.2881</v>
+        <v>1.2603</v>
       </c>
       <c r="F52" t="n">
-        <v>1.8717</v>
+        <v>1.8439</v>
       </c>
       <c r="G52" t="n">
         <v>-0.5836</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8717</v>
+        <v>1.8439</v>
       </c>
       <c r="I52" t="n">
         <v>1.9068</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.1949</v>
+        <v>1.1624</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1654</v>
+        <v>0.1609</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0614</v>
+        <v>0.0192</v>
       </c>
       <c r="E53" t="n">
-        <v>1.1949</v>
+        <v>1.1624</v>
       </c>
       <c r="F53" t="n">
-        <v>2.1949</v>
+        <v>2.1624</v>
       </c>
       <c r="G53" t="n">
         <v>-1</v>
       </c>
       <c r="H53" t="n">
-        <v>2.1949</v>
+        <v>2.1624</v>
       </c>
       <c r="I53" t="n">
         <v>2.2361</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.1151</v>
+        <v>1.111</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1543</v>
+        <v>0.1538</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0291</v>
+        <v>-0.0013</v>
       </c>
       <c r="E54" t="n">
-        <v>1.1151</v>
+        <v>1.111</v>
       </c>
       <c r="F54" t="n">
-        <v>1.1151</v>
+        <v>1.111</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.1151</v>
+        <v>1.111</v>
       </c>
       <c r="I54" t="n">
         <v>1.1203</v>
@@ -2940,7 +2940,7 @@
         <v>0.1232</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.0619</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="E55" t="n">
         <v>0.8899</v>
@@ -2986,7 +2986,7 @@
         <v>0.1204</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.0699</v>
+        <v>-0.0973</v>
       </c>
       <c r="E56" t="n">
         <v>0.87</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8486</v>
+        <v>0.8454</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1174</v>
+        <v>0.117</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.0785</v>
+        <v>-0.1071</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8486</v>
+        <v>0.8454</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8486</v>
+        <v>0.8454</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8486</v>
+        <v>0.8454</v>
       </c>
       <c r="I57" t="n">
         <v>0.8525</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8225</v>
+        <v>0.8164</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1138</v>
+        <v>0.113</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.0891</v>
+        <v>-0.1187</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8225</v>
+        <v>0.8164</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8225</v>
+        <v>0.8164</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8225</v>
+        <v>0.8164</v>
       </c>
       <c r="I58" t="n">
         <v>0.8302</v>
@@ -3124,7 +3124,7 @@
         <v>0.1076</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.1074</v>
+        <v>-0.1343</v>
       </c>
       <c r="E59" t="n">
         <v>0.7771</v>
@@ -3170,7 +3170,7 @@
         <v>0.1067</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.1099</v>
+        <v>-0.1368</v>
       </c>
       <c r="E60" t="n">
         <v>0.7709</v>
@@ -3206,93 +3206,93 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bubble</t>
+          <t>Viva</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7174</v>
+        <v>0.7109</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0993</v>
+        <v>0.0984</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.1315</v>
+        <v>-0.1607</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7174</v>
+        <v>0.7109</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8075</v>
+        <v>0.7109</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0901</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8075</v>
+        <v>0.7109</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8188</v>
+        <v>0.7109</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.0901</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L61" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7287</v>
+        <v>0.7109</v>
       </c>
       <c r="N61" t="n">
-        <v>364</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Viva</t>
+          <t>bubble</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7109</v>
+        <v>0.7084</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0984</v>
+        <v>0.098</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.1342</v>
+        <v>-0.1617</v>
       </c>
       <c r="E62" t="n">
-        <v>0.7109</v>
+        <v>0.7084</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7109</v>
+        <v>0.7985</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.0901</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7109</v>
+        <v>0.7985</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7109</v>
+        <v>0.8188</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.0901</v>
       </c>
       <c r="K62" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="M62" t="n">
-        <v>0.7109</v>
+        <v>0.7287</v>
       </c>
       <c r="N62" t="n">
-        <v>151</v>
+        <v>364</v>
       </c>
     </row>
     <row r="63">
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7033</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0973</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.1372</v>
+        <v>-0.1658</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7033</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7033</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7033</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="I63" t="n">
         <v>0.7099</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.66</v>
+        <v>0.6576</v>
       </c>
       <c r="C64" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.1547</v>
+        <v>-0.1819</v>
       </c>
       <c r="E64" t="n">
-        <v>0.66</v>
+        <v>0.6576</v>
       </c>
       <c r="F64" t="n">
-        <v>0.66</v>
+        <v>0.6576</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.66</v>
+        <v>0.6576</v>
       </c>
       <c r="I64" t="n">
         <v>0.6631</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5715</v>
+        <v>0.5672</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0791</v>
+        <v>0.0785</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.1905</v>
+        <v>-0.2179</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5715</v>
+        <v>0.5672</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5715</v>
+        <v>0.5672</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5715</v>
+        <v>0.5672</v>
       </c>
       <c r="I65" t="n">
         <v>0.5768</v>
@@ -3436,93 +3436,93 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>barce</t>
+          <t>motm</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.1931</v>
+        <v>-0.2221</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="F66" t="n">
-        <v>1.565</v>
+        <v>0.5567</v>
       </c>
       <c r="G66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.565</v>
+        <v>0.5567</v>
       </c>
       <c r="I66" t="n">
-        <v>1.5943</v>
+        <v>0.5567</v>
       </c>
       <c r="J66" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5567</v>
       </c>
       <c r="N66" t="n">
-        <v>219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>motm</t>
+          <t>barce</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5567</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.1965</v>
+        <v>-0.2281</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5567</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5567</v>
+        <v>1.5418</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5567</v>
+        <v>1.5418</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5567</v>
+        <v>1.5943</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K67" t="n">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M67" t="n">
-        <v>0.5567</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="N67" t="n">
-        <v>138</v>
+        <v>219</v>
       </c>
     </row>
     <row r="68">
@@ -3538,7 +3538,7 @@
         <v>0.0717</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.212</v>
+        <v>-0.2375</v>
       </c>
       <c r="E68" t="n">
         <v>0.5182</v>
@@ -3584,7 +3584,7 @@
         <v>0.0677</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.2237</v>
+        <v>-0.249</v>
       </c>
       <c r="E69" t="n">
         <v>0.4893</v>
@@ -3630,7 +3630,7 @@
         <v>0.0475</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.2827</v>
+        <v>-0.3072</v>
       </c>
       <c r="E70" t="n">
         <v>0.3432</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3255</v>
+        <v>0.3058</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0451</v>
+        <v>0.0423</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2899</v>
+        <v>-0.3221</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3255</v>
+        <v>0.3058</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3255</v>
+        <v>1.3058</v>
       </c>
       <c r="G71" t="n">
         <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>1.3255</v>
+        <v>1.3058</v>
       </c>
       <c r="I71" t="n">
         <v>1.3503</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.2204</v>
+        <v>0.2196</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0305</v>
+        <v>0.0304</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.3323</v>
+        <v>-0.3564</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2204</v>
+        <v>0.2196</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2204</v>
+        <v>0.2196</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2204</v>
+        <v>0.2196</v>
       </c>
       <c r="I72" t="n">
         <v>0.2214</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1874</v>
+        <v>0.1853</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0259</v>
+        <v>0.0256</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.3457</v>
+        <v>-0.3701</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1874</v>
+        <v>0.1853</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1874</v>
+        <v>0.1853</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1874</v>
+        <v>0.1853</v>
       </c>
       <c r="I73" t="n">
         <v>0.19</v>
@@ -3814,7 +3814,7 @@
         <v>0.0226</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.3554</v>
+        <v>-0.3789</v>
       </c>
       <c r="E74" t="n">
         <v>0.1633</v>
@@ -3860,7 +3860,7 @@
         <v>0.0219</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.3576</v>
+        <v>-0.381</v>
       </c>
       <c r="E75" t="n">
         <v>0.1579</v>
@@ -3906,7 +3906,7 @@
         <v>0.0208</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.3607</v>
+        <v>-0.3841</v>
       </c>
       <c r="E76" t="n">
         <v>0.1501</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.1396</v>
+        <v>0.139</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0193</v>
+        <v>0.0192</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.365</v>
+        <v>-0.3885</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1396</v>
+        <v>0.139</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1396</v>
+        <v>0.139</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1396</v>
+        <v>0.139</v>
       </c>
       <c r="I77" t="n">
         <v>0.1402</v>
@@ -3998,7 +3998,7 @@
         <v>0.0131</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.3832</v>
+        <v>-0.4063</v>
       </c>
       <c r="E78" t="n">
         <v>0.0945</v>
@@ -4044,7 +4044,7 @@
         <v>0.0126</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.3847</v>
+        <v>-0.4078</v>
       </c>
       <c r="E79" t="n">
         <v>0.0907</v>
@@ -4090,7 +4090,7 @@
         <v>0.0123</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.3853</v>
+        <v>-0.4084</v>
       </c>
       <c r="E80" t="n">
         <v>0.0892</v>
@@ -4136,7 +4136,7 @@
         <v>0.0108</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.3899</v>
+        <v>-0.4129</v>
       </c>
       <c r="E81" t="n">
         <v>0.0779</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="C82" t="n">
         <v>0.0057</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.4047</v>
+        <v>-0.4276</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.0412</v>
+        <v>0.0409</v>
       </c>
       <c r="I82" t="n">
         <v>0.0416</v>
@@ -4228,7 +4228,7 @@
         <v>0.002</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.4154</v>
+        <v>-0.438</v>
       </c>
       <c r="E83" t="n">
         <v>0.0148</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.0116</v>
+        <v>-0.0115</v>
       </c>
       <c r="C84" t="n">
         <v>-0.0016</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.426</v>
+        <v>-0.4485</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.0116</v>
+        <v>-0.0115</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0116</v>
+        <v>-0.0115</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.0116</v>
+        <v>-0.0115</v>
       </c>
       <c r="I84" t="n">
         <v>-0.0118</v>
@@ -4320,7 +4320,7 @@
         <v>-0.0026</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.4288</v>
+        <v>-0.4513</v>
       </c>
       <c r="E85" t="n">
         <v>-0.0185</v>
@@ -4360,25 +4360,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.01</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.4505</v>
+        <v>-0.4725</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.0722</v>
+        <v>-0.0717</v>
       </c>
       <c r="I86" t="n">
         <v>-0.07290000000000001</v>
@@ -4412,7 +4412,7 @@
         <v>-0.0116</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.4553</v>
+        <v>-0.4774</v>
       </c>
       <c r="E87" t="n">
         <v>-0.08400000000000001</v>
@@ -4458,7 +4458,7 @@
         <v>-0.0117</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.4554</v>
+        <v>-0.4775</v>
       </c>
       <c r="E88" t="n">
         <v>-0.0843</v>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.1081</v>
+        <v>-0.1127</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.015</v>
+        <v>-0.0156</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.465</v>
+        <v>-0.4888</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.1081</v>
+        <v>-0.1127</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6194</v>
+        <v>0.6148</v>
       </c>
       <c r="G89" t="n">
         <v>-0.7275</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6194</v>
+        <v>0.6148</v>
       </c>
       <c r="I89" t="n">
         <v>0.6252</v>
@@ -4550,7 +4550,7 @@
         <v>-0.0165</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.4696</v>
+        <v>-0.4915</v>
       </c>
       <c r="E90" t="n">
         <v>-0.1194</v>
@@ -4596,7 +4596,7 @@
         <v>-0.0378</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.5317</v>
+        <v>-0.5528</v>
       </c>
       <c r="E91" t="n">
         <v>-0.2732</v>
@@ -4642,7 +4642,7 @@
         <v>-0.0404</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.5393</v>
+        <v>-0.5602</v>
       </c>
       <c r="E92" t="n">
         <v>-0.2919</v>
@@ -4688,7 +4688,7 @@
         <v>-0.0492</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.5855</v>
       </c>
       <c r="E93" t="n">
         <v>-0.3555</v>
@@ -4734,7 +4734,7 @@
         <v>-0.0572</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.5883</v>
+        <v>-0.6085</v>
       </c>
       <c r="E94" t="n">
         <v>-0.4132</v>
@@ -4774,25 +4774,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-0.4699</v>
+        <v>-0.4682</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.065</v>
+        <v>-0.0648</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.6112</v>
+        <v>-0.6304</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.4699</v>
+        <v>-0.4682</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.4699</v>
+        <v>-0.4682</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.4699</v>
+        <v>-0.4682</v>
       </c>
       <c r="I95" t="n">
         <v>-0.4721</v>
@@ -4820,25 +4820,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.475</v>
+        <v>-0.4732</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0655</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.6133</v>
+        <v>-0.6324</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.475</v>
+        <v>-0.4732</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.475</v>
+        <v>-0.4732</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.475</v>
+        <v>-0.4732</v>
       </c>
       <c r="I96" t="n">
         <v>-0.4772</v>
@@ -4872,7 +4872,7 @@
         <v>-0.0725</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.633</v>
+        <v>-0.6526</v>
       </c>
       <c r="E97" t="n">
         <v>-0.5238</v>
@@ -4912,25 +4912,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-0.5765</v>
+        <v>-0.5722</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.0798</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.6543</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.5765</v>
+        <v>-0.5722</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.5765</v>
+        <v>-0.5722</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.5765</v>
+        <v>-0.5722</v>
       </c>
       <c r="I98" t="n">
         <v>-0.5819</v>
@@ -4964,7 +4964,7 @@
         <v>-0.0842</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.6673</v>
+        <v>-0.6864</v>
       </c>
       <c r="E99" t="n">
         <v>-0.6087</v>
@@ -5004,25 +5004,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-0.6133</v>
+        <v>-0.6111</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.0849</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.6691</v>
+        <v>-0.6874</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.6133</v>
+        <v>-0.6111</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.6133</v>
+        <v>-0.6111</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-0.6133</v>
+        <v>-0.6111</v>
       </c>
       <c r="I100" t="n">
         <v>-0.6162</v>
@@ -5056,7 +5056,7 @@
         <v>-0.0968</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.704</v>
+        <v>-0.7227</v>
       </c>
       <c r="E101" t="n">
         <v>-0.6997</v>
@@ -5102,7 +5102,7 @@
         <v>-0.09810000000000001</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.7077</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="E102" t="n">
         <v>-0.7087</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-0.8129</v>
+        <v>-0.8069</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.1125</v>
+        <v>-0.1117</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.7498</v>
+        <v>-0.7654</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.8129</v>
+        <v>-0.8069</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.8129</v>
+        <v>-0.8069</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.8129</v>
+        <v>-0.8069</v>
       </c>
       <c r="I103" t="n">
         <v>-0.8205</v>
@@ -5194,7 +5194,7 @@
         <v>-0.1137</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.7533</v>
+        <v>-0.7713</v>
       </c>
       <c r="E104" t="n">
         <v>-0.8217</v>
@@ -5240,7 +5240,7 @@
         <v>-0.1139</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.7538</v>
+        <v>-0.7718</v>
       </c>
       <c r="E105" t="n">
         <v>-0.8229</v>
@@ -5286,7 +5286,7 @@
         <v>-0.1146</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.756</v>
+        <v>-0.7739</v>
       </c>
       <c r="E106" t="n">
         <v>-0.8283</v>
@@ -5326,25 +5326,25 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-0.8642</v>
+        <v>-0.8662</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.1196</v>
+        <v>-0.1199</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.7705</v>
+        <v>-0.789</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.8642</v>
+        <v>-0.8662</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2668</v>
+        <v>0.2648</v>
       </c>
       <c r="G107" t="n">
         <v>-1.131</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2668</v>
+        <v>0.2648</v>
       </c>
       <c r="I107" t="n">
         <v>0.2692</v>
@@ -5372,25 +5372,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.8984</v>
+        <v>-0.8884</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.1243</v>
+        <v>-0.123</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.7843</v>
+        <v>-0.7978</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.8984</v>
+        <v>-0.8884</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.8984</v>
+        <v>-0.8884</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.8984</v>
+        <v>-0.8884</v>
       </c>
       <c r="I108" t="n">
         <v>-0.911</v>
@@ -5414,93 +5414,93 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>acAp</t>
+          <t>BL1TZ</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-0.899</v>
+        <v>-0.8978</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.1244</v>
+        <v>-0.1243</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.7845</v>
+        <v>-0.8016</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.899</v>
+        <v>-0.8978</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.899</v>
+        <v>-0.8978</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.899</v>
+        <v>-0.8978</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.899</v>
+        <v>-0.9054</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>112</v>
+        <v>167</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.899</v>
+        <v>-0.9054</v>
       </c>
       <c r="N109" t="n">
-        <v>112</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BL1TZ</t>
+          <t>acAp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-0.9012</v>
+        <v>-0.899</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.1247</v>
+        <v>-0.1244</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.7854</v>
+        <v>-0.8021</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.9012</v>
+        <v>-0.899</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.9012</v>
+        <v>-0.899</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.9012</v>
+        <v>-0.899</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.9054</v>
+        <v>-0.899</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.9054</v>
+        <v>-0.899</v>
       </c>
       <c r="N110" t="n">
-        <v>167</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111">
@@ -5516,7 +5516,7 @@
         <v>-0.125</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.7863</v>
+        <v>-0.8038</v>
       </c>
       <c r="E111" t="n">
         <v>-0.9033</v>
@@ -5562,7 +5562,7 @@
         <v>-0.1252</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.7867</v>
+        <v>-0.8042</v>
       </c>
       <c r="E112" t="n">
         <v>-0.9043</v>
@@ -5598,93 +5598,93 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tifa</t>
+          <t>natsu</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-1.1452</v>
+        <v>-1.1389</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.1585</v>
+        <v>-0.1576</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.884</v>
+        <v>-0.8976</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.1452</v>
+        <v>-1.1389</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.1452</v>
+        <v>-1.1389</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.1452</v>
+        <v>-1.1389</v>
       </c>
       <c r="I113" t="n">
-        <v>-1.1505</v>
+        <v>-1.1582</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-1.1505</v>
+        <v>-1.1582</v>
       </c>
       <c r="N113" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>natsu</t>
+          <t>tifa</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-1.1475</v>
+        <v>-1.1409</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.1588</v>
+        <v>-0.1579</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.8849</v>
+        <v>-0.8984</v>
       </c>
       <c r="E114" t="n">
-        <v>-1.1475</v>
+        <v>-1.1409</v>
       </c>
       <c r="F114" t="n">
-        <v>-1.1475</v>
+        <v>-1.1409</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.1475</v>
+        <v>-1.1409</v>
       </c>
       <c r="I114" t="n">
-        <v>-1.1582</v>
+        <v>-1.1505</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>-1.1582</v>
+        <v>-1.1505</v>
       </c>
       <c r="N114" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="115">
@@ -5694,25 +5694,25 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-1.1527</v>
+        <v>-1.1484</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.1595</v>
+        <v>-0.1589</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.887</v>
+        <v>-0.9014</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.1527</v>
+        <v>-1.1484</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.1527</v>
+        <v>-1.1484</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-1.1527</v>
+        <v>-1.1484</v>
       </c>
       <c r="I115" t="n">
         <v>-1.1581</v>
@@ -5746,7 +5746,7 @@
         <v>-0.1653</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.9038</v>
+        <v>-0.9197</v>
       </c>
       <c r="E116" t="n">
         <v>-1.1943</v>
@@ -5786,25 +5786,25 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-1.2164</v>
+        <v>-1.2073</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.1684</v>
+        <v>-0.1671</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.2164</v>
+        <v>-1.2073</v>
       </c>
       <c r="F117" t="n">
-        <v>-1.2164</v>
+        <v>-1.2073</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-1.2164</v>
+        <v>-1.2073</v>
       </c>
       <c r="I117" t="n">
         <v>-1.2277</v>
@@ -5838,7 +5838,7 @@
         <v>-0.1826</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.9542</v>
+        <v>-0.9694</v>
       </c>
       <c r="E118" t="n">
         <v>-1.319</v>
@@ -5878,25 +5878,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-1.3395</v>
+        <v>-1.3345</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.1854</v>
+        <v>-0.1847</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.9625</v>
+        <v>-0.9756</v>
       </c>
       <c r="E119" t="n">
-        <v>-1.3395</v>
+        <v>-1.3345</v>
       </c>
       <c r="F119" t="n">
-        <v>-1.3395</v>
+        <v>-1.3345</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>-1.3395</v>
+        <v>-1.3345</v>
       </c>
       <c r="I119" t="n">
         <v>-1.3457</v>
@@ -5930,7 +5930,7 @@
         <v>-0.1945</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.989</v>
+        <v>-1.0037</v>
       </c>
       <c r="E120" t="n">
         <v>-1.405</v>
@@ -5976,7 +5976,7 @@
         <v>-0.1981</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.9995000000000001</v>
+        <v>-1.0141</v>
       </c>
       <c r="E121" t="n">
         <v>-1.4311</v>
@@ -6022,7 +6022,7 @@
         <v>-0.2079</v>
       </c>
       <c r="D122" t="n">
-        <v>-1.0282</v>
+        <v>-1.0423</v>
       </c>
       <c r="E122" t="n">
         <v>-1.5021</v>
@@ -6068,7 +6068,7 @@
         <v>-0.2123</v>
       </c>
       <c r="D123" t="n">
-        <v>-1.0409</v>
+        <v>-1.0549</v>
       </c>
       <c r="E123" t="n">
         <v>-1.5336</v>
@@ -6108,25 +6108,25 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>-1.5554</v>
+        <v>-1.5496</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.2153</v>
+        <v>-0.2145</v>
       </c>
       <c r="D124" t="n">
-        <v>-1.0497</v>
+        <v>-1.0613</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.5554</v>
+        <v>-1.5496</v>
       </c>
       <c r="F124" t="n">
-        <v>-1.5554</v>
+        <v>-1.5496</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.5554</v>
+        <v>-1.5496</v>
       </c>
       <c r="I124" t="n">
         <v>-1.5626</v>
@@ -6160,7 +6160,7 @@
         <v>-0.2215</v>
       </c>
       <c r="D125" t="n">
-        <v>-1.0679</v>
+        <v>-1.0815</v>
       </c>
       <c r="E125" t="n">
         <v>-1.6004</v>
@@ -6206,7 +6206,7 @@
         <v>-0.2379</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.1157</v>
+        <v>-1.1286</v>
       </c>
       <c r="E126" t="n">
         <v>-1.7187</v>
@@ -6252,7 +6252,7 @@
         <v>-0.2401</v>
       </c>
       <c r="D127" t="n">
-        <v>-1.1221</v>
+        <v>-1.1349</v>
       </c>
       <c r="E127" t="n">
         <v>-1.7345</v>
@@ -6292,25 +6292,25 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-1.8018</v>
+        <v>-1.7951</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.2494</v>
+        <v>-0.2484</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.1492</v>
+        <v>-1.1591</v>
       </c>
       <c r="E128" t="n">
-        <v>-1.8018</v>
+        <v>-1.7951</v>
       </c>
       <c r="F128" t="n">
-        <v>-1.8018</v>
+        <v>-1.7951</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>-1.8018</v>
+        <v>-1.7951</v>
       </c>
       <c r="I128" t="n">
         <v>-1.8102</v>
@@ -6344,7 +6344,7 @@
         <v>-0.2659</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.1974</v>
+        <v>-1.2093</v>
       </c>
       <c r="E129" t="n">
         <v>-1.9211</v>
@@ -6390,7 +6390,7 @@
         <v>-0.2741</v>
       </c>
       <c r="D130" t="n">
-        <v>-1.2213</v>
+        <v>-1.2328</v>
       </c>
       <c r="E130" t="n">
         <v>-1.9802</v>
@@ -6436,7 +6436,7 @@
         <v>-0.2768</v>
       </c>
       <c r="D131" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E131" t="n">
         <v>-2</v>
@@ -6482,7 +6482,7 @@
         <v>-0.2768</v>
       </c>
       <c r="D132" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E132" t="n">
         <v>-2</v>
@@ -6528,7 +6528,7 @@
         <v>-0.2975</v>
       </c>
       <c r="D133" t="n">
-        <v>-1.2896</v>
+        <v>-1.3002</v>
       </c>
       <c r="E133" t="n">
         <v>-2.1493</v>
@@ -6574,7 +6574,7 @@
         <v>-0.3194</v>
       </c>
       <c r="D134" t="n">
-        <v>-1.3535</v>
+        <v>-1.3632</v>
       </c>
       <c r="E134" t="n">
         <v>-2.3075</v>
@@ -6620,7 +6620,7 @@
         <v>-0.3196</v>
       </c>
       <c r="D135" t="n">
-        <v>-1.3543</v>
+        <v>-1.364</v>
       </c>
       <c r="E135" t="n">
         <v>-2.3094</v>
@@ -6666,7 +6666,7 @@
         <v>-0.3221</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.3614</v>
+        <v>-1.371</v>
       </c>
       <c r="E136" t="n">
         <v>-2.327</v>
